--- a/Livrables/TourGuide+Performance+Graphs.xlsx
+++ b/Livrables/TourGuide+Performance+Graphs.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Locations" sheetId="1" state="visible" r:id="rId3"/>
@@ -142,16 +142,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -251,6 +255,7 @@
                 </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Roboto"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:rPr>
               <a:t>Get Location: Time / Users</a:t>
             </a:r>
@@ -304,12 +309,17 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -421,12 +431,17 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -485,19 +500,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>18</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>188</c:v>
+                  <c:v>84</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>400</c:v>
+                  <c:v>164</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -512,11 +527,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="67896166"/>
-        <c:axId val="81408602"/>
+        <c:axId val="11542797"/>
+        <c:axId val="71392243"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="67896166"/>
+        <c:axId val="11542797"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -542,11 +557,12 @@
                 </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Roboto"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81408602"/>
+        <c:crossAx val="71392243"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -554,7 +570,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="81408602"/>
+        <c:axId val="71392243"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -588,6 +604,7 @@
                     </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Roboto"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:rPr>
                   <a:t>Time (Seconds)</a:t>
                 </a:r>
@@ -622,11 +639,12 @@
                 </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Roboto"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67896166"/>
+        <c:crossAx val="11542797"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -657,6 +675,7 @@
               </a:solidFill>
               <a:uFillTx/>
               <a:latin typeface="Roboto"/>
+              <a:ea typeface="DejaVu Sans"/>
             </a:defRPr>
           </a:pPr>
         </a:p>
@@ -701,6 +720,7 @@
                 </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Roboto"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:rPr>
               <a:t>Get Rewards: Time / Users</a:t>
             </a:r>
@@ -754,12 +774,17 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -859,12 +884,17 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -914,16 +944,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>101</c:v>
+                  <c:v>502</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -938,11 +968,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="10833044"/>
-        <c:axId val="69213023"/>
+        <c:axId val="26823086"/>
+        <c:axId val="6673944"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="10833044"/>
+        <c:axId val="26823086"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -968,11 +998,12 @@
                 </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Roboto"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69213023"/>
+        <c:crossAx val="6673944"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -980,7 +1011,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="69213023"/>
+        <c:axId val="6673944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1014,6 +1045,7 @@
                     </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Roboto"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:rPr>
                   <a:t>Time (Seconds)</a:t>
                 </a:r>
@@ -1048,11 +1080,12 @@
                 </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Roboto"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10833044"/>
+        <c:crossAx val="26823086"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1083,6 +1116,7 @@
               </a:solidFill>
               <a:uFillTx/>
               <a:latin typeface="Roboto"/>
+              <a:ea typeface="DejaVu Sans"/>
             </a:defRPr>
           </a:pPr>
         </a:p>
@@ -1114,9 +1148,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>811080</xdr:colOff>
+      <xdr:colOff>810720</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>133200</xdr:rowOff>
+      <xdr:rowOff>132840</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1125,7 +1159,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="5130000" y="200160"/>
-        <a:ext cx="5714640" cy="3533400"/>
+        <a:ext cx="5714280" cy="3533040"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1149,9 +1183,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>821160</xdr:colOff>
+      <xdr:colOff>820800</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>123480</xdr:rowOff>
+      <xdr:rowOff>123120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1160,7 +1194,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4875840" y="190440"/>
-        <a:ext cx="5714640" cy="3533400"/>
+        <a:ext cx="5714280" cy="3533040"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1288,92 +1322,92 @@
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1"/>
+      <c r="A1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="3"/>
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="D4" s="1" t="n">
-        <v>3</v>
+      <c r="D4" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>5000</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>376</v>
       </c>
-      <c r="D5" s="1" t="n">
-        <v>18</v>
+      <c r="D5" s="2" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>10000</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>762</v>
       </c>
-      <c r="D6" s="1" t="n">
-        <v>38</v>
+      <c r="D6" s="2" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>50000</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>3791</v>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>188</v>
+      <c r="D7" s="2" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>100000</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>7579</v>
       </c>
-      <c r="D8" s="1" t="n">
-        <v>400</v>
+      <c r="D8" s="2" t="n">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -1397,66 +1431,66 @@
   <dimension ref="A2:D6"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.2"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="D3" s="1" t="n">
-        <v>2</v>
+      <c r="D3" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>472</v>
       </c>
-      <c r="D4" s="1" t="n">
-        <v>2</v>
+      <c r="D4" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>10000</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>5820</v>
       </c>
-      <c r="D5" s="1" t="n">
-        <v>10</v>
+      <c r="D5" s="2" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>100000</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>64020</v>
       </c>
-      <c r="D6" s="1" t="n">
-        <v>101</v>
+      <c r="D6" s="2" t="n">
+        <v>502</v>
       </c>
     </row>
   </sheetData>
